--- a/artfynd/A 51403-2024 artfynd.xlsx
+++ b/artfynd/A 51403-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1603292</v>
+        <v>111951992</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Hästmyren, Jmt</t>
+          <t>Ögonfägnaden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546348.854141943</v>
+        <v>546434</v>
       </c>
       <c r="R2" t="n">
-        <v>7045020.490499573</v>
+        <v>7044966</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111952116</v>
+        <v>111947505</v>
       </c>
       <c r="B3" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546682</v>
+        <v>546217</v>
       </c>
       <c r="R3" t="n">
-        <v>7044541</v>
+        <v>7044622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,31 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111952003</v>
+        <v>111947527</v>
       </c>
       <c r="B4" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546640</v>
+        <v>546095</v>
       </c>
       <c r="R4" t="n">
-        <v>7044491</v>
+        <v>7044771</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,31 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111951996</v>
+        <v>111952001</v>
       </c>
       <c r="B5" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546568</v>
+        <v>546461</v>
       </c>
       <c r="R5" t="n">
-        <v>7044544</v>
+        <v>7044833</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111952118</v>
+        <v>111952002</v>
       </c>
       <c r="B6" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1082,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546617</v>
+        <v>546200</v>
       </c>
       <c r="R6" t="n">
-        <v>7044493</v>
+        <v>7044790</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111951993</v>
+        <v>111951998</v>
       </c>
       <c r="B7" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546354</v>
+        <v>546561</v>
       </c>
       <c r="R7" t="n">
-        <v>7044818</v>
+        <v>7044696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,15 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111951998</v>
+        <v>111951999</v>
       </c>
       <c r="B8" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546560</v>
+        <v>546617</v>
       </c>
       <c r="R8" t="n">
-        <v>7044696</v>
+        <v>7044493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,12 +1377,7 @@
         <v>111952000</v>
       </c>
       <c r="B9" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,53 +1475,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111951992</v>
+        <v>1603292</v>
       </c>
       <c r="B10" t="n">
-        <v>73827</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ögonfägnaden, Jmt</t>
+          <t>Söder om Hästmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546434</v>
+        <v>546349</v>
       </c>
       <c r="R10" t="n">
-        <v>7044966</v>
+        <v>7045020</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,12 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2012-05-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2012-05-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,12 +1560,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,37 +1576,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111952120</v>
+        <v>111952003</v>
       </c>
       <c r="B11" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546461</v>
+        <v>546640</v>
       </c>
       <c r="R11" t="n">
-        <v>7044833</v>
+        <v>7044491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,15 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111951997</v>
+        <v>111951993</v>
       </c>
       <c r="B12" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546718</v>
+        <v>546354</v>
       </c>
       <c r="R12" t="n">
-        <v>7044652</v>
+        <v>7044819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111952123</v>
+        <v>111951994</v>
       </c>
       <c r="B13" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546199</v>
+        <v>546681</v>
       </c>
       <c r="R13" t="n">
-        <v>7044790</v>
+        <v>7044541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,15 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111951995</v>
+        <v>111952016</v>
       </c>
       <c r="B14" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1997,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546257</v>
+        <v>546825</v>
       </c>
       <c r="R14" t="n">
-        <v>7044676</v>
+        <v>7044669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 51403-2024 artfynd.xlsx
+++ b/artfynd/A 51403-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951992</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111947527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951999</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952000</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1603292</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951993</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951994</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,8 +2042,28 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>